--- a/docs/downloads/05/tbl_water_alaotra_analamiranga.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_analamiranga.xlsx
@@ -387,12 +387,6 @@
           <t>Autre ____________________________</t>
         </is>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -441,12 +429,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -477,12 +459,6 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>4.3</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,12 +591,6 @@
         <is>
           <t>Alaotra - Tous</t>
         </is>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
